--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-03-2026.xlsx
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£32.98</t>
+          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Max retries exceeded with url: /120mm-celotex-xr4120-pir-insulation-board-2400x1200mm-17-p.asp (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000002B9A359D750&gt;, 'Connection to onlineinsulation-sales.com timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£745.00</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
